--- a/Q3/3.2/common_outliers_table3.2.xlsx
+++ b/Q3/3.2/common_outliers_table3.2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,6 +428,2296 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>183</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>351</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>352</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>659</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>968</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>969</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>970</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>974</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>975</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>abe</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1025</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>be</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1105</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1211</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1212</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1235</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1236</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1405</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1406</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1497</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>1498</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1631</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1632</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1633</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1669</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1670</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1758</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1759</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>1760</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1913</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>1914</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>1981</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1982</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2550</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2551</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2552</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2636</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2637</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2720</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2721</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2748</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2749</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2754</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2755</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2875</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>abe</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2876</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2905</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2906</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2913</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2914</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2937</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>abe</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2938</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>abe</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3030</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3031</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3032</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>3259</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3260</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3352</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>3353</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>3487</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>3513</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>3514</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>3541</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>3549</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>3550</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3555</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>3556</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>3557</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>3558</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>3640</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>3858</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>be</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>3859</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>be</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>3994</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>4011</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>4012</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4034</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>4035</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>4048</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>4049</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>4061</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>4124</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>4125</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>4172</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>4173</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>4275</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>4276</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>4277</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>4338</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>4339</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>4470</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>4536</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>4660</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>4661</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>4662</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>4864</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>4865</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>4866</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>4881</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>4882</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>5082</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>5083</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>5109</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>5110</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>5132</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>5133</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>5205</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>5206</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>5312</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>5313</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>5314</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>5370</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>5371</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>5472</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>5473</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>5474</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>5541</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>5542</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>5543</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>5568</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>5569</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>5841</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>6083</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>6084</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>6118</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>6119</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>6143</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>6144</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>6327</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>6328</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>6386</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>6387</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>6472</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>6507</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>6527</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>6528</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>6529</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>6763</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>6764</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>6770</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>6771</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>6945</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>7060</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>7061</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>7062</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>7214</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>7215</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>7249</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>7250</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>7324</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>7325</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>7425</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>7426</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>7427</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>7597</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>7598</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>7599</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>7692</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>7693</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>7754</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>7755</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>7778</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>7884</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>7885</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>7886</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>7928</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>7929</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>7968</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>7969</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>8013</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>8014</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>8030</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>bde</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>8031</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>bde</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>8104</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>8105</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>8106</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>8185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>8186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>8207</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>8208</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>8252</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>8253</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>8254</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>8273</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>8274</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>8325</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>8326</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>8592</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>8677</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>8678</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>8909</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>8910</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>8948</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>8949</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>9034</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>9035</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>9036</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>9037</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>9041</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>9042</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>9061</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>9062</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>9188</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>9334</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>9335</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>9408</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>9409</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>9418</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>9429</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>9430</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>9490</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>9491</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>9517</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>9518</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>9642</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>9643</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>9773</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>9774</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>9799</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>9800</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>9801</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Q3/3.2/common_outliers_table3.2.xlsx
+++ b/Q3/3.2/common_outliers_table3.2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B230"/>
+  <dimension ref="A1:B233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -430,47 +430,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>183</v>
+        <v>293</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>351</v>
+        <v>294</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>352</v>
+        <v>308</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>659</v>
+        <v>309</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>968</v>
+        <v>352</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -480,67 +480,67 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>969</v>
+        <v>659</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>970</v>
+        <v>660</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>974</v>
+        <v>686</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>975</v>
+        <v>687</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1024</v>
+        <v>856</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>abe</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1025</v>
+        <v>857</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>be</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1105</v>
+        <v>969</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -550,57 +550,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1106</v>
+        <v>1024</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1211</v>
+        <v>1025</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1212</v>
+        <v>1040</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1235</v>
+        <v>1041</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1236</v>
+        <v>1055</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1377</v>
+        <v>1105</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
@@ -634,13 +634,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1497</v>
+        <v>1444</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -650,167 +650,167 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1501</v>
+        <v>1514</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1631</v>
+        <v>1515</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1632</v>
+        <v>1570</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1633</v>
+        <v>1571</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1669</v>
+        <v>1602</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1670</v>
+        <v>1603</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1758</v>
+        <v>1604</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1759</v>
+        <v>1631</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1760</v>
+        <v>1632</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ade</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1913</v>
+        <v>1669</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1914</v>
+        <v>1670</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1981</v>
+        <v>1675</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1982</v>
+        <v>1676</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1995</v>
+        <v>1758</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2020</v>
+        <v>1759</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -820,127 +820,127 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2021</v>
+        <v>1760</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2022</v>
+        <v>1769</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2550</v>
+        <v>1770</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2551</v>
+        <v>1845</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2552</v>
+        <v>1846</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2636</v>
+        <v>1917</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2637</v>
+        <v>1918</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2720</v>
+        <v>1994</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2721</v>
+        <v>1995</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2748</v>
+        <v>2020</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2749</v>
+        <v>2021</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2754</v>
+        <v>2022</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2755</v>
+        <v>2083</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -950,97 +950,97 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2875</v>
+        <v>2332</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>abe</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2876</v>
+        <v>2333</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2905</v>
+        <v>2550</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2906</v>
+        <v>2551</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>abde</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2913</v>
+        <v>2553</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2914</v>
+        <v>2554</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2937</v>
+        <v>2636</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>abe</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2938</v>
+        <v>2637</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>abe</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>3030</v>
+        <v>2638</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>3031</v>
+        <v>2721</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1050,137 +1050,137 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>3032</v>
+        <v>2748</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ade</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>3259</v>
+        <v>2749</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>3260</v>
+        <v>2773</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>3352</v>
+        <v>2774</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>3353</v>
+        <v>2787</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>3487</v>
+        <v>2788</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>3513</v>
+        <v>2874</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>3514</v>
+        <v>2875</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>3541</v>
+        <v>2876</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>3549</v>
+        <v>2913</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3550</v>
+        <v>2914</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>3555</v>
+        <v>2937</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>3556</v>
+        <v>2938</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>3557</v>
+        <v>3031</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -1190,77 +1190,77 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3558</v>
+        <v>3144</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3640</v>
+        <v>3145</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>3858</v>
+        <v>3259</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>be</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3859</v>
+        <v>3260</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>be</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>3994</v>
+        <v>3352</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>ae</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>4011</v>
+        <v>3394</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>4012</v>
+        <v>3395</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4034</v>
+        <v>3424</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>4035</v>
+        <v>3425</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -1280,147 +1280,147 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4048</v>
+        <v>3447</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>4049</v>
+        <v>3448</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4061</v>
+        <v>3449</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ac</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4124</v>
+        <v>3513</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>4125</v>
+        <v>3514</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>4172</v>
+        <v>3540</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>4173</v>
+        <v>3541</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>4275</v>
+        <v>3779</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>ae</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>4276</v>
+        <v>3858</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>abde</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>4277</v>
+        <v>3859</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>abde</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>4338</v>
+        <v>4021</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ad</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>4339</v>
+        <v>4034</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>4470</v>
+        <v>4035</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4536</v>
+        <v>4048</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>ae</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>4660</v>
+        <v>4060</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -1430,47 +1430,47 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>4661</v>
+        <v>4091</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>4662</v>
+        <v>4092</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>4864</v>
+        <v>4124</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>4865</v>
+        <v>4125</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>4866</v>
+        <v>4173</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -1480,117 +1480,117 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>4881</v>
+        <v>4207</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>4882</v>
+        <v>4208</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>5082</v>
+        <v>4275</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>5083</v>
+        <v>4276</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>5109</v>
+        <v>4277</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>5110</v>
+        <v>4338</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>5132</v>
+        <v>4339</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>5133</v>
+        <v>4470</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>5205</v>
+        <v>4471</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>5206</v>
+        <v>4642</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>5312</v>
+        <v>4643</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>5313</v>
+        <v>4661</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -1600,67 +1600,67 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>5314</v>
+        <v>4662</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>5370</v>
+        <v>4679</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>5371</v>
+        <v>4680</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>5472</v>
+        <v>4697</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>5473</v>
+        <v>4698</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>5474</v>
+        <v>4699</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>5541</v>
+        <v>4737</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>5542</v>
+        <v>4865</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -1680,87 +1680,87 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>5543</v>
+        <v>4881</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>5568</v>
+        <v>4882</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>5569</v>
+        <v>4912</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>5841</v>
+        <v>4913</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>6083</v>
+        <v>5060</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>6084</v>
+        <v>5061</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>6118</v>
+        <v>5109</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>6119</v>
+        <v>5110</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>6143</v>
+        <v>5147</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -1770,57 +1770,57 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>6144</v>
+        <v>5312</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>6327</v>
+        <v>5313</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>6328</v>
+        <v>5314</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>6386</v>
+        <v>5472</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>6387</v>
+        <v>5473</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>6471</v>
+        <v>5542</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -1830,37 +1830,37 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>6472</v>
+        <v>5690</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ce</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>6507</v>
+        <v>5728</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>6527</v>
+        <v>5729</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>6528</v>
+        <v>6083</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -1870,17 +1870,17 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>6529</v>
+        <v>6143</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>6763</v>
+        <v>6144</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -1890,47 +1890,47 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>6764</v>
+        <v>6208</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>6770</v>
+        <v>6209</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>6771</v>
+        <v>6386</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>6945</v>
+        <v>6387</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>7060</v>
+        <v>6472</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -1940,27 +1940,27 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>7061</v>
+        <v>6487</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>7062</v>
+        <v>6488</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>7214</v>
+        <v>6528</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -1970,447 +1970,447 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>7215</v>
+        <v>6763</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>7249</v>
+        <v>6764</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>7250</v>
+        <v>6770</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>7324</v>
+        <v>6771</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>7325</v>
+        <v>6945</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>7425</v>
+        <v>6946</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>7426</v>
+        <v>6957</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>7427</v>
+        <v>6958</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>7597</v>
+        <v>7061</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>abde</t>
+          <t>ae</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>7598</v>
+        <v>7115</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>abde</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>7599</v>
+        <v>7116</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>abde</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>7692</v>
+        <v>7150</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>7693</v>
+        <v>7151</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>7754</v>
+        <v>7160</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>7755</v>
+        <v>7161</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>7778</v>
+        <v>7249</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>7884</v>
+        <v>7250</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>7885</v>
+        <v>7426</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>abde</t>
+          <t>ae</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>7886</v>
+        <v>7597</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>abde</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>7928</v>
+        <v>7598</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>7929</v>
+        <v>7599</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>7968</v>
+        <v>7710</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>7969</v>
+        <v>7711</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>8013</v>
+        <v>7754</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>abde</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>8014</v>
+        <v>7755</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>8030</v>
+        <v>7778</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>bde</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>8031</v>
+        <v>7779</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>bde</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>8104</v>
+        <v>7855</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>ae</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>8105</v>
+        <v>7884</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>8106</v>
+        <v>7885</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>8185</v>
+        <v>7886</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>8186</v>
+        <v>7928</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ad</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>8207</v>
+        <v>7968</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>8208</v>
+        <v>7969</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>8252</v>
+        <v>7987</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>8253</v>
+        <v>7988</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>8254</v>
+        <v>8013</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>8273</v>
+        <v>8014</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>8274</v>
+        <v>8030</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>8325</v>
+        <v>8031</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>8326</v>
+        <v>8032</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>8592</v>
+        <v>8104</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>8677</v>
+        <v>8105</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>8678</v>
+        <v>8106</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>8909</v>
+        <v>8208</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -2420,177 +2420,177 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>8910</v>
+        <v>8253</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ade</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>8948</v>
+        <v>8254</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>8949</v>
+        <v>8325</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>9034</v>
+        <v>8326</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>9035</v>
+        <v>8677</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>9036</v>
+        <v>8678</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>abde</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>9037</v>
+        <v>8948</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>ae</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>9041</v>
+        <v>8983</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>9042</v>
+        <v>9016</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>9061</v>
+        <v>9017</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>9062</v>
+        <v>9028</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>9188</v>
+        <v>9029</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>9334</v>
+        <v>9035</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>abde</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>9335</v>
+        <v>9036</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>9408</v>
+        <v>9037</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>9409</v>
+        <v>9061</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ade</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>9418</v>
+        <v>9062</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ab</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>9429</v>
+        <v>9157</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>9430</v>
+        <v>9334</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -2610,109 +2610,139 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>9490</v>
+        <v>9408</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>ae</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>9491</v>
+        <v>9418</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ade</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>9517</v>
+        <v>9419</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bd</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>9518</v>
+        <v>9429</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>9642</v>
+        <v>9430</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>9643</v>
+        <v>9490</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>9773</v>
+        <v>9491</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>bde</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>9774</v>
+        <v>9740</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>9799</v>
+        <v>9741</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>be</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>9800</v>
+        <v>9752</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>de</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>9801</v>
+        <v>9753</v>
       </c>
       <c r="B230" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>9773</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>9774</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>9800</v>
+      </c>
+      <c r="B233" t="inlineStr">
         <is>
           <t>ae</t>
         </is>

--- a/Q3/3.2/common_outliers_table3.2.xlsx
+++ b/Q3/3.2/common_outliers_table3.2.xlsx
@@ -1,40 +1,408 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="3">
+  <si>
+    <t>Serial No.</t>
+  </si>
+  <si>
+    <t>Common Abnormals</t>
+  </si>
+  <si>
+    <t>ade</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,85 +410,315 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -403,62 +1001,53 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Serial No.</t>
-        </is>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Common Abnormals</t>
-        </is>
+      <c r="B1" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:2">
+      <c r="A2" s="1">
         <v>1406</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ade</t>
-        </is>
+      <c r="B2" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:2">
+      <c r="A3" s="1">
         <v>1759</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ade</t>
-        </is>
+      <c r="B3" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:2">
+      <c r="A4" s="1">
         <v>9035</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ade</t>
-        </is>
+      <c r="B4" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>